--- a/cds_files/Clemson_CDS_2025-2026.xlsx
+++ b/cds_files/Clemson_CDS_2025-2026.xlsx
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.075</v>
+        <v>0.375</v>
       </c>
       <c r="C3" t="n">
-        <v>0.075</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.925</v>
+        <v>0.625</v>
       </c>
       <c r="C4" t="n">
-        <v>0.925</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="5">
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
